--- a/artfynd/A 52436-2024 artfynd.xlsx
+++ b/artfynd/A 52436-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>80116366</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498760.0299540717</v>
+        <v>498760</v>
       </c>
       <c r="R2" t="n">
-        <v>6695038.062709901</v>
+        <v>6695038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +754,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,19 +788,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80116416</v>
+        <v>80116352</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,8 +816,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -846,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498727.8335547045</v>
+        <v>498756</v>
       </c>
       <c r="R3" t="n">
-        <v>6695000.011698977</v>
+        <v>6695041</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,19 +867,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,16 +904,11 @@
         <v>80116374</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -974,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498772.9031815281</v>
+        <v>498773</v>
       </c>
       <c r="R4" t="n">
-        <v>6695038.058338086</v>
+        <v>6695038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,19 +980,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,19 +1014,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80116352</v>
+        <v>80116416</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1084,16 +1042,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498756.0699767236</v>
+        <v>498728</v>
       </c>
       <c r="R5" t="n">
-        <v>6695041.029928611</v>
+        <v>6695000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,19 +1085,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52436-2024 artfynd.xlsx
+++ b/artfynd/A 52436-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80116366</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80116352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80116374</t>
         </is>
       </c>
     </row>
@@ -1116,8 +1136,19 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80116416</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>